--- a/NBFC-MF/Borrowers/Sunita_Group_Soibam_L.xlsx
+++ b/NBFC-MF/Borrowers/Sunita_Group_Soibam_L.xlsx
@@ -929,31 +929,33 @@
       <c r="K6" s="26"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" s="19"/>
-      <c r="B7" s="23" t="str">
+      <c r="A7" s="19">
+        <v>46279</v>
+      </c>
+      <c r="B7" s="23">
         <f t="shared" si="3"/>
-        <v/>
+        <v>6</v>
       </c>
       <c r="C7" s="20"/>
-      <c r="D7" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E7" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F7" s="21" t="str">
+      <c r="D7" s="21">
+        <f t="shared" si="0"/>
+        <v>7000</v>
+      </c>
+      <c r="E7" s="21">
+        <f t="shared" si="1"/>
+        <v>1483.8948408557112</v>
+      </c>
+      <c r="F7" s="21">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G7" s="21" t="str">
+        <v>5516.1051591442883</v>
+      </c>
+      <c r="G7" s="21">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H7" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>68487.847000612353</v>
+      </c>
+      <c r="H7" s="21">
+        <f t="shared" si="2"/>
+        <v>31512.152999387647</v>
       </c>
       <c r="J7" s="4" t="s">
         <v>6</v>
@@ -963,31 +965,33 @@
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A8" s="2"/>
-      <c r="B8" s="22" t="str">
+      <c r="A8" s="2">
+        <v>46286</v>
+      </c>
+      <c r="B8" s="22">
         <f t="shared" si="3"/>
-        <v/>
+        <v>7</v>
       </c>
       <c r="C8" s="3"/>
-      <c r="D8" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E8" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F8" s="1" t="str">
+      <c r="D8" s="1">
+        <f t="shared" si="0"/>
+        <v>7000</v>
+      </c>
+      <c r="E8" s="1">
+        <f t="shared" si="1"/>
+        <v>1373.2883158203774</v>
+      </c>
+      <c r="F8" s="1">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G8" s="1" t="str">
+        <v>5626.7116841796224</v>
+      </c>
+      <c r="G8" s="1">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H8" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>62861.13531643273</v>
+      </c>
+      <c r="H8" s="1">
+        <f t="shared" si="2"/>
+        <v>37138.86468356727</v>
       </c>
       <c r="J8" s="4" t="s">
         <v>14</v>
@@ -1126,7 +1130,7 @@
       </c>
       <c r="K12" s="9">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
@@ -1161,7 +1165,7 @@
       </c>
       <c r="K13" s="11">
         <f>(K10*K9)-K9*K12</f>
-        <v>84000</v>
+        <v>70000</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
@@ -1196,7 +1200,7 @@
       </c>
       <c r="K14" s="11">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>74003.952159756635</v>
+        <v>62861.13531643273</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1231,7 +1235,7 @@
       </c>
       <c r="K15" s="13">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>25996.047840243365</v>
+        <v>37138.86468356727</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">

--- a/NBFC-MF/Borrowers/Sunita_Group_Soibam_L.xlsx
+++ b/NBFC-MF/Borrowers/Sunita_Group_Soibam_L.xlsx
@@ -1002,31 +1002,33 @@
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" s="19"/>
-      <c r="B9" s="23" t="str">
+      <c r="A9" s="19">
+        <v>46293</v>
+      </c>
+      <c r="B9" s="23">
         <f t="shared" si="3"/>
-        <v/>
+        <v>8</v>
       </c>
       <c r="C9" s="20"/>
-      <c r="D9" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E9" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F9" s="21" t="str">
+      <c r="D9" s="21">
+        <f t="shared" si="0"/>
+        <v>7000</v>
+      </c>
+      <c r="E9" s="21">
+        <f t="shared" si="1"/>
+        <v>1260.4639571819057</v>
+      </c>
+      <c r="F9" s="21">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G9" s="21" t="str">
+        <v>5739.5360428180938</v>
+      </c>
+      <c r="G9" s="21">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H9" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>57121.599273614636</v>
+      </c>
+      <c r="H9" s="21">
+        <f t="shared" si="2"/>
+        <v>42878.400726385364</v>
       </c>
       <c r="J9" s="4" t="s">
         <v>7</v>
@@ -1130,7 +1132,7 @@
       </c>
       <c r="K12" s="9">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
@@ -1165,7 +1167,7 @@
       </c>
       <c r="K13" s="11">
         <f>(K10*K9)-K9*K12</f>
-        <v>70000</v>
+        <v>63000</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
@@ -1200,7 +1202,7 @@
       </c>
       <c r="K14" s="11">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>62861.13531643273</v>
+        <v>57121.599273614636</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1235,7 +1237,7 @@
       </c>
       <c r="K15" s="13">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>37138.86468356727</v>
+        <v>42878.400726385364</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">

--- a/NBFC-MF/Borrowers/Sunita_Group_Soibam_L.xlsx
+++ b/NBFC-MF/Borrowers/Sunita_Group_Soibam_L.xlsx
@@ -1038,31 +1038,33 @@
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A10" s="2"/>
-      <c r="B10" s="22" t="str">
+      <c r="A10" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B10" s="22">
         <f t="shared" si="3"/>
-        <v/>
+        <v>9</v>
       </c>
       <c r="C10" s="3"/>
-      <c r="D10" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E10" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F10" s="1" t="str">
+      <c r="D10" s="1">
+        <f t="shared" si="0"/>
+        <v>7000</v>
+      </c>
+      <c r="E10" s="1">
+        <f t="shared" si="1"/>
+        <v>1145.3772939121209</v>
+      </c>
+      <c r="F10" s="1">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G10" s="1" t="str">
+        <v>5854.6227060878791</v>
+      </c>
+      <c r="G10" s="1">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H10" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>51266.976567526755</v>
+      </c>
+      <c r="H10" s="1">
+        <f t="shared" si="2"/>
+        <v>48733.023432473245</v>
       </c>
       <c r="J10" s="4" t="s">
         <v>8</v>
@@ -1072,31 +1074,33 @@
       </c>
     </row>
     <row r="11" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="19"/>
-      <c r="B11" s="23" t="str">
+      <c r="A11" s="19">
+        <v>46307</v>
+      </c>
+      <c r="B11" s="23">
         <f t="shared" si="3"/>
-        <v/>
+        <v>10</v>
       </c>
       <c r="C11" s="20"/>
-      <c r="D11" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E11" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F11" s="21" t="str">
+      <c r="D11" s="21">
+        <f t="shared" si="0"/>
+        <v>7000</v>
+      </c>
+      <c r="E11" s="21">
+        <f t="shared" si="1"/>
+        <v>1027.9829632692656</v>
+      </c>
+      <c r="F11" s="21">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G11" s="21" t="str">
+        <v>5972.0170367307346</v>
+      </c>
+      <c r="G11" s="21">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H11" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>45294.959530796019</v>
+      </c>
+      <c r="H11" s="21">
+        <f t="shared" si="2"/>
+        <v>54705.040469203981</v>
       </c>
       <c r="J11" s="14"/>
     </row>
@@ -1132,7 +1136,7 @@
       </c>
       <c r="K12" s="9">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
@@ -1167,7 +1171,7 @@
       </c>
       <c r="K13" s="11">
         <f>(K10*K9)-K9*K12</f>
-        <v>63000</v>
+        <v>49000</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
@@ -1202,7 +1206,7 @@
       </c>
       <c r="K14" s="11">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>57121.599273614636</v>
+        <v>45294.959530796019</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1237,7 +1241,7 @@
       </c>
       <c r="K15" s="13">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>42878.400726385364</v>
+        <v>54705.040469203981</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
